--- a/data/05_modelado/results/results_ensambles.xlsx
+++ b/data/05_modelado/results/results_ensambles.xlsx
@@ -547,55 +547,55 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.7881854927351709</v>
+        <v>0.8251813955488357</v>
       </c>
       <c r="E2" t="n">
-        <v>0.006441266113322218</v>
+        <v>0.004311349696083499</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9307603492573528</v>
+        <v>0.9509454529582371</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003369638422393489</v>
+        <v>0.002072358484271208</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8306076336509782</v>
+        <v>0.8560836957613203</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7501884161812543</v>
+        <v>0.7965917875586352</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8821012114439259</v>
+        <v>0.9012862840552307</v>
       </c>
       <c r="K2" t="n">
-        <v>1883.698</v>
+        <v>1390.184</v>
       </c>
       <c r="L2" t="n">
-        <v>5.18</v>
+        <v>6.83</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7988</v>
+        <v>0.8273</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9358</v>
+        <v>0.9535</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8892</v>
+        <v>0.9132</v>
       </c>
       <c r="P2" t="n">
-        <v>0.8356</v>
+        <v>0.8483000000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.7651</v>
+        <v>0.8073</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8873</v>
+        <v>0.9014</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7208</v>
+        <v>0.7584</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2855</v>
+        <v>0.248</v>
       </c>
     </row>
     <row r="3">
@@ -615,55 +615,55 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.7881854927351709</v>
+        <v>0.8251813955488357</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006441266113322218</v>
+        <v>0.004311349696083499</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9307603492573528</v>
+        <v>0.9509454529582371</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003369638422393489</v>
+        <v>0.002072358484271208</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8306076336509782</v>
+        <v>0.8560836957613203</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7501884161812543</v>
+        <v>0.7965917875586352</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8821012114439259</v>
+        <v>0.9012862840552307</v>
       </c>
       <c r="K3" t="n">
-        <v>1503.055</v>
+        <v>1442.575</v>
       </c>
       <c r="L3" t="n">
-        <v>5.04</v>
+        <v>6.68</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7988</v>
+        <v>0.8273</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9358</v>
+        <v>0.9535</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8892</v>
+        <v>0.9132</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8356</v>
+        <v>0.8483000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.7651</v>
+        <v>0.8073</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8873</v>
+        <v>0.9014</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7208</v>
+        <v>0.7584</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2855</v>
+        <v>0.248</v>
       </c>
     </row>
     <row r="4">
@@ -683,55 +683,55 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7878604723957467</v>
+        <v>0.8231545772598434</v>
       </c>
       <c r="E4" t="n">
-        <v>0.005884427512063179</v>
+        <v>0.005135717713261351</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9291065767684914</v>
+        <v>0.9488747938285949</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003556340034782772</v>
+        <v>0.002773654872964864</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7810071136288008</v>
+        <v>0.8153806817385323</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7950660405783427</v>
+        <v>0.8312981693136481</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8748139294281561</v>
+        <v>0.8955233038299155</v>
       </c>
       <c r="K4" t="n">
-        <v>3609.714</v>
+        <v>6342.906</v>
       </c>
       <c r="L4" t="n">
-        <v>5.04</v>
+        <v>6.68</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7965</v>
+        <v>0.8196</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9339</v>
+        <v>0.9514</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8864</v>
+        <v>0.9105</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7798</v>
+        <v>0.7985</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.8139</v>
+        <v>0.8419</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8784</v>
+        <v>0.8915999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7098</v>
+        <v>0.7422</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3021</v>
+        <v>0.262</v>
       </c>
     </row>
     <row r="5">
@@ -751,55 +751,55 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7780450447876784</v>
+        <v>0.8158304750648921</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004658825352115823</v>
+        <v>0.003505436513881685</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9253609085385284</v>
+        <v>0.9449883476342735</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00382201184570054</v>
+        <v>0.002471744951359491</v>
       </c>
       <c r="H5" t="n">
-        <v>0.817508047908289</v>
+        <v>0.8422739919119419</v>
       </c>
       <c r="I5" t="n">
-        <v>0.742434555164138</v>
+        <v>0.7912527232499509</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8761152727355659</v>
+        <v>0.895523366029672</v>
       </c>
       <c r="K5" t="n">
-        <v>390.557</v>
+        <v>656.528</v>
       </c>
       <c r="L5" t="n">
-        <v>5.08</v>
+        <v>6.94</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7867</v>
+        <v>0.8176</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9304</v>
+        <v>0.9483</v>
       </c>
       <c r="O5" t="n">
-        <v>0.879</v>
+        <v>0.9036999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8159</v>
+        <v>0.8313</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.7595</v>
+        <v>0.8043</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8796</v>
+        <v>0.895</v>
       </c>
       <c r="S5" t="n">
-        <v>0.703</v>
+        <v>0.7439</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2995</v>
+        <v>0.2636</v>
       </c>
     </row>
     <row r="6">
@@ -819,55 +819,55 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.7780450447876784</v>
+        <v>0.8158304750648921</v>
       </c>
       <c r="E6" t="n">
-        <v>0.004658825352115823</v>
+        <v>0.003505436513881685</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9253609085385284</v>
+        <v>0.9449883476342735</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00382201184570054</v>
+        <v>0.002471744951359491</v>
       </c>
       <c r="H6" t="n">
-        <v>0.817508047908289</v>
+        <v>0.8422739919119419</v>
       </c>
       <c r="I6" t="n">
-        <v>0.742434555164138</v>
+        <v>0.7912527232499509</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8761152727355659</v>
+        <v>0.895523366029672</v>
       </c>
       <c r="K6" t="n">
-        <v>513.6319999999999</v>
+        <v>481.012</v>
       </c>
       <c r="L6" t="n">
-        <v>5.02</v>
+        <v>6.67</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7867</v>
+        <v>0.8176</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9304</v>
+        <v>0.9483</v>
       </c>
       <c r="O6" t="n">
-        <v>0.879</v>
+        <v>0.9036999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8159</v>
+        <v>0.8313</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.7595</v>
+        <v>0.8043</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8796</v>
+        <v>0.895</v>
       </c>
       <c r="S6" t="n">
-        <v>0.703</v>
+        <v>0.7439</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2995</v>
+        <v>0.2636</v>
       </c>
     </row>
     <row r="7">
@@ -887,55 +887,55 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.7841880159374434</v>
+        <v>0.8200644394623776</v>
       </c>
       <c r="E7" t="n">
-        <v>0.006443181769639867</v>
+        <v>0.004151467032299099</v>
       </c>
       <c r="F7" t="n">
-        <v>0.924575927827392</v>
+        <v>0.944761622362701</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00403692349496118</v>
+        <v>0.002644847308576271</v>
       </c>
       <c r="H7" t="n">
-        <v>0.786120607203334</v>
+        <v>0.8147946097158089</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7824804858996843</v>
+        <v>0.8257047330629403</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8740702829605149</v>
+        <v>0.8940361352941461</v>
       </c>
       <c r="K7" t="n">
-        <v>1877.52</v>
+        <v>1731.173</v>
       </c>
       <c r="L7" t="n">
-        <v>5.03</v>
+        <v>6.67</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7889</v>
+        <v>0.8236</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9296</v>
+        <v>0.9481000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8798</v>
+        <v>0.9049</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7783</v>
+        <v>0.8088</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.7997</v>
+        <v>0.8388</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8748</v>
+        <v>0.8949</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6999</v>
+        <v>0.7487</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3085</v>
+        <v>0.2711</v>
       </c>
     </row>
     <row r="8">
@@ -955,61 +955,61 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.7484429778343922</v>
+        <v>0.7857642160266411</v>
       </c>
       <c r="E8" t="n">
-        <v>0.007045173669809596</v>
+        <v>0.007518361017691409</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9088978328670831</v>
+        <v>0.9298593588287318</v>
       </c>
       <c r="G8" t="n">
-        <v>0.005891850327644642</v>
+        <v>0.002940966150935203</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7184990455026184</v>
+        <v>0.7545141466774683</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7810824499515732</v>
+        <v>0.8201101659112517</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8464826244979962</v>
+        <v>0.8692367882533686</v>
       </c>
       <c r="K8" t="n">
-        <v>31.037</v>
+        <v>71.434</v>
       </c>
       <c r="L8" t="n">
-        <v>5</v>
+        <v>6.64</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7551</v>
+        <v>0.7861</v>
       </c>
       <c r="N8" t="n">
-        <v>0.9133</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8498</v>
+        <v>0.8787</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7111</v>
+        <v>0.7417</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.8048</v>
+        <v>0.8363</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8473000000000001</v>
+        <v>0.8669</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6447000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4631</v>
+        <v>0.445</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AdaBoost</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1023,61 +1023,61 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.7346021919440012</v>
+        <v>0.7680192654030435</v>
       </c>
       <c r="E9" t="n">
-        <v>0.008623850829764327</v>
+        <v>0.01137668644677119</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9073468196712163</v>
+        <v>0.9282010462024315</v>
       </c>
       <c r="G9" t="n">
-        <v>0.005419817326884455</v>
+        <v>0.003252072683053184</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8117269994874123</v>
+        <v>0.830378849828832</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6712423189609281</v>
+        <v>0.7151064945219965</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8582315848981755</v>
+        <v>0.8738103778220548</v>
       </c>
       <c r="K9" t="n">
-        <v>19.987</v>
+        <v>20.731</v>
       </c>
       <c r="L9" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7396</v>
+        <v>0.7713</v>
       </c>
       <c r="N9" t="n">
-        <v>0.9117</v>
+        <v>0.9339</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8479</v>
+        <v>0.8772</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8075</v>
+        <v>0.8138</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.6823</v>
+        <v>0.7331</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8595</v>
+        <v>0.8729</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6443</v>
+        <v>0.6836</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4205</v>
+        <v>0.2924</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AdaBoost</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1091,61 +1091,61 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.7346021919440012</v>
+        <v>0.7680192654030435</v>
       </c>
       <c r="E10" t="n">
-        <v>0.008623850829764327</v>
+        <v>0.01137668644677119</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9073468196712163</v>
+        <v>0.9282010462024315</v>
       </c>
       <c r="G10" t="n">
-        <v>0.005419817326884455</v>
+        <v>0.003252072683053184</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8117269994874123</v>
+        <v>0.830378849828832</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6712423189609281</v>
+        <v>0.7151064945219965</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8582315848981755</v>
+        <v>0.8738103778220548</v>
       </c>
       <c r="K10" t="n">
-        <v>18.325</v>
+        <v>18.024</v>
       </c>
       <c r="L10" t="n">
-        <v>5</v>
+        <v>6.64</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7396</v>
+        <v>0.7713</v>
       </c>
       <c r="N10" t="n">
-        <v>0.9117</v>
+        <v>0.9339</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8479</v>
+        <v>0.8772</v>
       </c>
       <c r="P10" t="n">
-        <v>0.8075</v>
+        <v>0.8138</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.6823</v>
+        <v>0.7331</v>
       </c>
       <c r="R10" t="n">
-        <v>0.8595</v>
+        <v>0.8729</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6443</v>
+        <v>0.6836</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4205</v>
+        <v>0.2924</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>AdaBoost</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1159,61 +1159,61 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.702128629123305</v>
+        <v>0.7531045823849295</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01701650551630925</v>
+        <v>0.007630946081345134</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9062719112250728</v>
+        <v>0.9240837379510936</v>
       </c>
       <c r="G11" t="n">
-        <v>0.003155251030847576</v>
+        <v>0.003312467116935505</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8475576441688654</v>
+        <v>0.8313178176975002</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6025966294304055</v>
+        <v>0.6885311292611743</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8510560067341603</v>
+        <v>0.8680099187878512</v>
       </c>
       <c r="K11" t="n">
-        <v>14.083</v>
+        <v>31.611</v>
       </c>
       <c r="L11" t="n">
-        <v>5.15</v>
+        <v>6.64</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7071</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>0.914</v>
+        <v>0.9301</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8516</v>
+        <v>0.8646</v>
       </c>
       <c r="P11" t="n">
-        <v>0.8773</v>
+        <v>0.8269</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.5923</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8565</v>
+        <v>0.8703</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6168</v>
+        <v>0.6724</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3278</v>
+        <v>0.4058</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>AdaBoost</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1227,55 +1227,55 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.702128629123305</v>
+        <v>0.7531045823849295</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01701650551630925</v>
+        <v>0.007630946081345134</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9062719112250728</v>
+        <v>0.9240837379510936</v>
       </c>
       <c r="G12" t="n">
-        <v>0.003155251030847576</v>
+        <v>0.003312467116935505</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8475576441688654</v>
+        <v>0.8313178176975002</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6025966294304055</v>
+        <v>0.6885311292611743</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8510560067341603</v>
+        <v>0.8680099187878512</v>
       </c>
       <c r="K12" t="n">
-        <v>6.348</v>
+        <v>33.396</v>
       </c>
       <c r="L12" t="n">
-        <v>5</v>
+        <v>6.64</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7071</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>0.914</v>
+        <v>0.9301</v>
       </c>
       <c r="O12" t="n">
-        <v>0.8516</v>
+        <v>0.8646</v>
       </c>
       <c r="P12" t="n">
-        <v>0.8773</v>
+        <v>0.8269</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.5923</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8565</v>
+        <v>0.8703</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6168</v>
+        <v>0.6724</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3278</v>
+        <v>0.4058</v>
       </c>
     </row>
     <row r="13">
@@ -1295,55 +1295,55 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.7375513828142146</v>
+        <v>0.7685357021647838</v>
       </c>
       <c r="E13" t="n">
-        <v>0.008723856147437736</v>
+        <v>0.004666734889156638</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8990202201092504</v>
+        <v>0.9239479055348996</v>
       </c>
       <c r="G13" t="n">
-        <v>0.004263840517042803</v>
+        <v>0.001883537286232897</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7015943218934325</v>
+        <v>0.7118950317075459</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7779020332791846</v>
+        <v>0.8353645661257998</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8381168401694321</v>
+        <v>0.8528036747616194</v>
       </c>
       <c r="K13" t="n">
-        <v>13.502</v>
+        <v>35.549</v>
       </c>
       <c r="L13" t="n">
-        <v>5</v>
+        <v>6.64</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7378</v>
+        <v>0.7708</v>
       </c>
       <c r="N13" t="n">
-        <v>0.9045</v>
+        <v>0.93</v>
       </c>
       <c r="O13" t="n">
-        <v>0.8245</v>
+        <v>0.8705000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6812</v>
+        <v>0.7163</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.8048</v>
+        <v>0.8343</v>
       </c>
       <c r="R13" t="n">
-        <v>0.8327</v>
+        <v>0.8549</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6162</v>
+        <v>0.6655</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3713</v>
+        <v>0.3238</v>
       </c>
     </row>
   </sheetData>
